--- a/output/heldback_firm_G/OsterquillData/Studies/OT-23-S0046/Raw_Observations/OT-23-S0046_SafetyPharm_RESULTS_032323.xlsx
+++ b/output/heldback_firm_G/OsterquillData/Studies/OT-23-S0046/Raw_Observations/OT-23-S0046_SafetyPharm_RESULTS_032323.xlsx
@@ -174,7 +174,7 @@
   <commentList>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
-        <t>Geometric mean of accepted cells; censored replicates excluded</t>
+        <t>Geometric mean of finite cell IC50s when they are the majority of accepted cells; otherwise &gt;30 µM (&gt;10 µM where precipitation limited the top concentration). n = accepted cells (finite).</t>
       </text>
     </comment>
   </commentList>
@@ -528,13 +528,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -551,6 +551,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -590,12 +591,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Study Director</t>
+          <t>Study lead</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Dr N. Takamori</t>
+          <t>Dr N. Takamori (Head of Toxicology)</t>
         </is>
       </c>
     </row>
@@ -636,259 +637,272 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>hERG median IC50 (µM)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>12</v>
+          <t>Regulatory status</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Exploratory, non-GLP (QA data-integrity audit only)</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>E-4031 IC50 (nM)</t>
+          <t>hERG median IC50 (µM)</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Compounds with any CYP &gt;50%</t>
+          <t>E-4031 IC50 (nM)</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>Compounds with any CYP &gt;50%</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>Ketoconazole IC50 (µM)</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B15" s="3" t="n">
         <v>0.023</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Study summary (benchmark)</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Study summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>OT-23-S0046</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Project</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Avernelwick Pharmaceuticals Ltd</t>
+          <t>OT-23-S0046</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Compounds tested</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>44</v>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Avernelwick Pharmaceuticals Ltd</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Series / chemotype</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Avernelwick aminopyrimidine regioisomer series 02 (Aminopyrimidine regioisomer)</t>
-        </is>
+          <t>Compounds tested</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Assays</t>
+          <t>Series / chemotype</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>hERG patch clamp, CYP inhibition panel (1A2/2C9/2C19/2D6/3A4) at 10 µM</t>
+          <t>Avernelwick aminopyrimidine regioisomer series 02 (Aminopyrimidine regioisomer)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Turnaround (calendar days)</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>15</v>
+          <t>Assays</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>hERG patch clamp, CYP inhibition panel (1A2/2C9/2C19/2D6/3A4) at 10 µM</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>USD 25,000</t>
-        </is>
+          <t>Turnaround (calendar days)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>hERG IC50 &lt;1 µM</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>0</v>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>USD 25,000</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>hERG IC50 1-10 µM</t>
+          <t>hERG IC50 &lt;1 µM</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>hERG IC50 ≥10 µM</t>
+          <t>hERG IC50 1-10 µM</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>hERG median IC50 (µM)</t>
+          <t>hERG IC50 ≥10 µM</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>E-4031 control IC50 (nM)</t>
+          <t>hERG median IC50 (µM)</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>CYP1A2 &gt;50% inhibition @10 µM</t>
+          <t>E-4031 control IC50 (nM)</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>CYP2C9 &gt;50% inhibition @10 µM</t>
+          <t>CYP1A2 &gt;50% inhibition @10 µM</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>CYP2C19 &gt;50% inhibition @10 µM</t>
+          <t>CYP2C9 &gt;50% inhibition @10 µM</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>CYP2D6 &gt;50% inhibition @10 µM</t>
+          <t>CYP2C19 &gt;50% inhibition @10 µM</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>CYP3A4 &gt;50% inhibition @10 µM</t>
+          <t>CYP2D6 &gt;50% inhibition @10 µM</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Compounds with any CYP &gt;50%</t>
+          <t>CYP3A4 &gt;50% inhibition @10 µM</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>Compounds with any CYP &gt;50%</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
           <t>Ketoconazole (3A4) IC50 (µM)</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B37" s="2" t="n">
         <v>0.023</v>
       </c>
     </row>
@@ -898,6 +912,7 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -905,28 +920,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="13.5" customWidth="1" min="3" max="3"/>
-    <col width="13.5" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="17.1" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="18.8" customWidth="1" min="2" max="2"/>
+    <col width="18.8" customWidth="1" min="3" max="3"/>
+    <col width="18.8" customWidth="1" min="4" max="4"/>
+    <col width="19.85" customWidth="1" min="5" max="5"/>
+    <col width="21.95" customWidth="1" min="6" max="6"/>
+    <col width="18.8" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>hERG (IKr) safety pharmacology: tail-current IC50, 6-point, top 30 µM</t>
-        </is>
-      </c>
-    </row>
+          <t>hERG (IKr) safety pharmacology: tail-current IC50 per cell, 6-point, top 30 µM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -935,22 +951,22 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>IC50 rep 1 (µM)</t>
+          <t>IC50 cell 1 (µM)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>IC50 rep 2 (µM)</t>
+          <t>IC50 cell 2 (µM)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>IC50 rep 3 (µM)</t>
+          <t>IC50 cell 3 (µM)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>IC50 mean (µM)</t>
+          <t>IC50 geomean (µM)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -960,7 +976,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>n cells (finite)</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -994,8 +1010,10 @@
       <c r="F4" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>2</v>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2 (0)</t>
+        </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
     </row>
@@ -1020,8 +1038,10 @@
       <c r="F5" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>3</v>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
     </row>
@@ -1044,8 +1064,10 @@
       <c r="F6" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>2</v>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
     </row>
@@ -1068,8 +1090,10 @@
       <c r="F7" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="G7" s="2" t="n">
-        <v>2</v>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
     </row>
@@ -1092,8 +1116,10 @@
       <c r="F8" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>2</v>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
     </row>
@@ -1116,8 +1142,10 @@
       <c r="F9" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>2</v>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
     </row>
@@ -1142,8 +1170,10 @@
       <c r="F10" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>3</v>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
     </row>
@@ -1170,8 +1200,10 @@
       <c r="F11" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>2</v>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2 (1)</t>
+        </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
     </row>
@@ -1194,8 +1226,10 @@
       <c r="F12" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G12" s="2" t="n">
-        <v>2</v>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
     </row>
@@ -1218,8 +1252,10 @@
       <c r="F13" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>2</v>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
     </row>
@@ -1242,8 +1278,10 @@
       <c r="F14" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>2</v>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
     </row>
@@ -1266,8 +1304,10 @@
       <c r="F15" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>2</v>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
     </row>
@@ -1290,8 +1330,10 @@
       <c r="F16" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>2</v>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
     </row>
@@ -1314,8 +1356,10 @@
       <c r="F17" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="G17" s="2" t="n">
-        <v>2</v>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
     </row>
@@ -1338,8 +1382,10 @@
       <c r="F18" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>2</v>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
     </row>
@@ -1362,8 +1408,10 @@
       <c r="F19" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="G19" s="2" t="n">
-        <v>2</v>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
     </row>
@@ -1386,8 +1434,10 @@
       <c r="F20" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="G20" s="2" t="n">
-        <v>2</v>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
     </row>
@@ -1410,8 +1460,10 @@
       <c r="F21" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="G21" s="2" t="n">
-        <v>2</v>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
     </row>
@@ -1434,8 +1486,10 @@
       <c r="F22" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="G22" s="2" t="n">
-        <v>2</v>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
     </row>
@@ -1458,8 +1512,10 @@
       <c r="F23" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="G23" s="2" t="n">
-        <v>2</v>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
     </row>
@@ -1490,8 +1546,10 @@
       <c r="F24" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="G24" s="2" t="n">
-        <v>3</v>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3 (1)</t>
+        </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
     </row>
@@ -1514,8 +1572,10 @@
       <c r="F25" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="G25" s="2" t="n">
-        <v>2</v>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
     </row>
@@ -1538,8 +1598,10 @@
       <c r="F26" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G26" s="2" t="n">
-        <v>2</v>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
     </row>
@@ -1562,8 +1624,10 @@
       <c r="F27" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="G27" s="2" t="n">
-        <v>2</v>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
     </row>
@@ -1586,8 +1650,10 @@
       <c r="F28" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="G28" s="2" t="n">
-        <v>2</v>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
     </row>
@@ -1610,8 +1676,10 @@
       <c r="F29" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="G29" s="2" t="n">
-        <v>2</v>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
     </row>
@@ -1634,8 +1702,10 @@
       <c r="F30" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="G30" s="2" t="n">
-        <v>2</v>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
     </row>
@@ -1658,8 +1728,10 @@
       <c r="F31" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="G31" s="2" t="n">
-        <v>2</v>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
     </row>
@@ -1686,8 +1758,10 @@
       <c r="F32" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="G32" s="2" t="n">
-        <v>2</v>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2 (1)</t>
+        </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
     </row>
@@ -1710,8 +1784,10 @@
       <c r="F33" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="G33" s="2" t="n">
-        <v>2</v>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
     </row>
@@ -1734,8 +1810,10 @@
       <c r="F34" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="G34" s="2" t="n">
-        <v>2</v>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
     </row>
@@ -1758,8 +1836,10 @@
       <c r="F35" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="G35" s="2" t="n">
-        <v>2</v>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
     </row>
@@ -1782,8 +1862,10 @@
       <c r="F36" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="G36" s="2" t="n">
-        <v>2</v>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
     </row>
@@ -1808,8 +1890,10 @@
       <c r="F37" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="G37" s="2" t="n">
-        <v>3</v>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
     </row>
@@ -1832,8 +1916,10 @@
       <c r="F38" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="G38" s="2" t="n">
-        <v>2</v>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
     </row>
@@ -1860,8 +1946,10 @@
       <c r="F39" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="G39" s="2" t="n">
-        <v>3</v>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>3 (2)</t>
+        </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
     </row>
@@ -1884,8 +1972,10 @@
       <c r="F40" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="G40" s="2" t="n">
-        <v>2</v>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
     </row>
@@ -1908,8 +1998,10 @@
       <c r="F41" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="G41" s="2" t="n">
-        <v>2</v>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
     </row>
@@ -1932,12 +2024,14 @@
       <c r="F42" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="G42" s="2" t="n">
-        <v>2</v>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Run 2 rejected (E-4031 outside range); repeated</t>
+          <t>First run rejected (E-4031 outside range); repeated</t>
         </is>
       </c>
     </row>
@@ -1960,8 +2054,10 @@
       <c r="F43" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="G43" s="2" t="n">
-        <v>2</v>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
     </row>
@@ -1984,8 +2080,10 @@
       <c r="F44" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="G44" s="2" t="n">
-        <v>2</v>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
     </row>
@@ -2008,8 +2106,10 @@
       <c r="F45" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="G45" s="2" t="n">
-        <v>2</v>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
     </row>
@@ -2032,8 +2132,10 @@
       <c r="F46" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="G46" s="2" t="n">
-        <v>2</v>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
     </row>
@@ -2056,15 +2158,18 @@
       <c r="F47" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="G47" s="2" t="n">
-        <v>2</v>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Precipitation observed at top concentration</t>
-        </is>
-      </c>
-    </row>
+          <t>Precipitation at 30 µM; 30 µM point excluded from fits</t>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
@@ -2072,8 +2177,16 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Compound IC50 = geometric mean of finite cell IC50s when they are the majority of accepted cells; otherwise reported as &gt;30 µM (or &gt;10 µM where solubility-limited)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -2083,15 +2196,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13.55" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
@@ -2103,6 +2216,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -3103,6 +3217,7 @@
         <v>47</v>
       </c>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
@@ -3119,6 +3234,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -3127,15 +3243,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3156,10 +3275,20 @@
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Historical mean</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
           <t>Acceptance</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3181,10 +3310,16 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>nM</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>5-50 nM</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3206,10 +3341,18 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3231,10 +3374,18 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3256,10 +3407,18 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3281,10 +3440,18 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3306,23 +3473,33 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>All runs met control validity criteria. Checked by Lucia Moretti.</t>
+          <t>All accepted runs met control validity criteria; rejected runs were repeated as noted on the hERG sheet. Checked by Lucia Moretti.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>